--- a/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:50</t>
+          <t>2026-08-25 10:24:35</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:51</t>
+          <t>2026-08-25 10:24:36</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:52</t>
+          <t>2026-08-25 10:24:38</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:54</t>
+          <t>2026-08-25 10:24:39</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:54</t>
+          <t>2026-08-25 10:24:39</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:54</t>
+          <t>2026-08-25 10:24:39</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:54</t>
+          <t>2026-08-25 10:24:39</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:54</t>
+          <t>2026-08-25 10:24:39</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:08</t>
+          <t>2026-08-25 10:24:55</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:09</t>
+          <t>2026-08-25 10:24:56</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15626,7 +15626,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:11</t>
+          <t>2026-08-25 10:24:57</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:12</t>
+          <t>2026-08-25 10:24:59</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:12</t>
+          <t>2026-08-25 10:24:59</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:12</t>
+          <t>2026-08-25 10:24:59</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:12</t>
+          <t>2026-08-25 10:24:59</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:12</t>
+          <t>2026-08-25 10:24:59</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17395,7 +17395,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17578,7 +17578,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17639,7 +17639,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17761,7 +17761,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -18005,7 +18005,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18493,7 +18493,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18554,7 +18554,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18981,7 +18981,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19042,7 +19042,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19469,7 +19469,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19591,7 +19591,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19896,7 +19896,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19957,7 +19957,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -20018,7 +20018,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20140,7 +20140,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20323,7 +20323,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21177,7 +21177,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22413,7 +22413,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">

--- a/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M317"/>
+  <dimension ref="A1:M367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:10</t>
+          <t>2026-08-25 21:09:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:11</t>
+          <t>2026-08-25 21:09:31</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:13</t>
+          <t>2026-08-25 21:09:32</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:14</t>
+          <t>2026-08-25 21:09:34</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:14</t>
+          <t>2026-08-25 21:09:34</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:14</t>
+          <t>2026-08-25 21:09:34</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:14</t>
+          <t>2026-08-25 21:09:34</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:14</t>
+          <t>2026-08-25 21:09:34</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:29</t>
+          <t>2026-08-25 21:09:51</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:30</t>
+          <t>2026-08-25 21:09:52</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:31</t>
+          <t>2026-08-25 21:09:53</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:32</t>
+          <t>2026-08-25 21:09:55</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:32</t>
+          <t>2026-08-25 21:09:55</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:32</t>
+          <t>2026-08-25 21:09:55</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:32</t>
+          <t>2026-08-25 21:09:55</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:32</t>
+          <t>2026-08-25 21:09:55</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16313,17 +16313,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -16331,38 +16331,38 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2330台灣積體電路製造</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>-0.87%14285</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>14285</v>
+        <v>2400</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>8.77%260,000</t>
+          <t>13.92%588,000</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>13.92%</t>
         </is>
       </c>
       <c r="K261" t="n">
-        <v>260000</v>
+        <v>588000</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -16374,17 +16374,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -16392,38 +16392,38 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>2376技嘉科技</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>+1.05%2400</t>
+          <t>+1.91%347.5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>2400</v>
+        <v>347.5</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>7.40%1,306,000</t>
+          <t>4.92%1,448,000</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>4.92%</t>
         </is>
       </c>
       <c r="K262" t="n">
-        <v>1306000</v>
+        <v>1448000</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -16435,17 +16435,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -16453,38 +16453,38 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>+3.33%2950</t>
+          <t>-1.8%246</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>2950</v>
+        <v>246</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>6.97%1,001,000</t>
+          <t>4.34%1,737,000</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="K263" t="n">
-        <v>1001000</v>
+        <v>1737000</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -16496,17 +16496,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -16514,38 +16514,38 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>4904遠傳電信</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>+1.86%1095</t>
+          <t>+0.99%102.5</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>1095</v>
+        <v>102.5</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>6.42%2,482,000</t>
+          <t>3.88%3,832,000</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="K264" t="n">
-        <v>2482000</v>
+        <v>3832000</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -16557,17 +16557,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -16575,38 +16575,38 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2412中華電信</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>+3.04%5595</t>
+          <t>0%136.5</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>+3.04%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>5595</v>
+        <v>136.5</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>6.14%465,000</t>
+          <t>3.85%2,828,000</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="K265" t="n">
-        <v>465000</v>
+        <v>2828000</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -16618,17 +16618,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -16636,34 +16636,34 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>+1.22%2075</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>2075</v>
+        <v>6440</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>5.69%1,161,000</t>
+          <t>3.33%53,000</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K266" t="n">
-        <v>1161000</v>
+        <v>53000</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -16679,17 +16679,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -16715,20 +16715,20 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>5.15%1,074,000</t>
+          <t>2.56%124,000</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K267" t="n">
-        <v>1074000</v>
+        <v>124000</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -16740,17 +16740,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -16758,38 +16758,38 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>+6.11%1215</t>
+          <t>+0.97%5205</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>1215</v>
+        <v>5205</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>4.67%1,630,000</t>
+          <t>2.52%49,000</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K268" t="n">
-        <v>1630000</v>
+        <v>49000</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -16801,17 +16801,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -16819,38 +16819,38 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>1504東元電機</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>+6.22%5720</t>
+          <t>-0.98%70.8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>+6.22%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5720</v>
+        <v>70.8</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>4.63%343,000</t>
+          <t>2.47%3,473,000</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K269" t="n">
-        <v>343000</v>
+        <v>3473000</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -16862,17 +16862,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -16880,38 +16880,38 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3105穩懋半導體</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>+0.63%5600</t>
+          <t>+6.76%379</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+6.76%</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>5600</v>
+        <v>379</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>3.54%268,000</t>
+          <t>2.32%656,000</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K270" t="n">
-        <v>268000</v>
+        <v>656000</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -16923,17 +16923,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -16941,38 +16941,38 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>7750新代科技</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>+1.37%594</t>
+          <t>+9.81%2350</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>+1.37%</t>
+          <t>+9.81%</t>
         </is>
       </c>
       <c r="H271" t="n">
-        <v>594</v>
+        <v>2350</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>3.13%2,231,000</t>
+          <t>2.30%108,000</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K271" t="n">
-        <v>2231000</v>
+        <v>108000</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -16984,17 +16984,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -17002,38 +17002,38 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3081聯亞光電工業</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>+1.71%178.5</t>
+          <t>+7.05%2960</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+7.05%</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>178.5</v>
+        <v>2960</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>3.05%7,245,000</t>
+          <t>2.29%83,000</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K272" t="n">
-        <v>7245000</v>
+        <v>83000</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -17045,17 +17045,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -17063,38 +17063,38 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>+1.4%109</t>
+          <t>+9.93%1605</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H273" t="n">
-        <v>109</v>
+        <v>1605</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2.80%10,877,000</t>
+          <t>2.15%148,000</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K273" t="n">
-        <v>10877000</v>
+        <v>148000</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -17106,17 +17106,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -17124,38 +17124,38 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>+9.96%419.5</t>
+          <t>-0.78%50.6</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H274" t="n">
-        <v>419.5</v>
+        <v>50.6</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2.73%2,753,000</t>
+          <t>2.13%4,181,000</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K274" t="n">
-        <v>2753000</v>
+        <v>4181000</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -17167,17 +17167,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -17185,38 +17185,38 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>+3.99%404</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>+3.99%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>404</v>
+        <v>591</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2.56%2,682,000</t>
+          <t>1.98%335,000</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K275" t="n">
-        <v>2682000</v>
+        <v>335000</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -17228,17 +17228,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -17246,38 +17246,38 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>-1.44%1710</t>
+          <t>-0.72%6210</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>1710</v>
+        <v>6210</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2.55%632,000</t>
+          <t>1.93%31,000</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K276" t="n">
-        <v>632000</v>
+        <v>31000</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -17289,17 +17289,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -17307,38 +17307,38 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>+4.72%188.5</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>+4.72%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>188.5</v>
+        <v>2950</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2.42%5,445,000</t>
+          <t>1.93%68,000</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K277" t="n">
-        <v>5445000</v>
+        <v>68000</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -17350,17 +17350,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17386,16 +17386,16 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2.35%266,000</t>
+          <t>1.88%50,000</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="K278" t="n">
-        <v>266000</v>
+        <v>50000</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -17411,17 +17411,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -17429,38 +17429,38 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2610中華航空</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>+3.82%5570</t>
+          <t>-0.49%20.4</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>+3.82%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>5570</v>
+        <v>20.4</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>2.16%164,000</t>
+          <t>1.79%8,783,000</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K279" t="n">
-        <v>164000</v>
+        <v>8783000</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -17472,17 +17472,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -17490,38 +17490,38 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>+3.48%3865</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>+3.48%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>3865</v>
+        <v>1095</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>1.96%215,000</t>
+          <t>1.71%160,000</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K280" t="n">
-        <v>215000</v>
+        <v>160000</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -17533,17 +17533,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -17551,38 +17551,38 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>+5.16%835</t>
+          <t>+1.02%1490</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>+5.16%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>835</v>
+        <v>1490</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>1.66%844,013</t>
+          <t>1.59%108,000</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K281" t="n">
-        <v>844013</v>
+        <v>108000</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -17594,17 +17594,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -17612,38 +17612,38 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6147頎邦科技</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>+2.22%6440</t>
+          <t>+7.64%169</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>6440</v>
+        <v>169</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>1.17%77,000</t>
+          <t>1.59%1,019,000</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K282" t="n">
-        <v>77000</v>
+        <v>1019000</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -17655,17 +17655,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -17673,38 +17673,38 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>+1.95%444</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>444</v>
+        <v>14285</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>1.05%1,000,000</t>
+          <t>1.58%11,000</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K283" t="n">
-        <v>1000000</v>
+        <v>11000</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -17716,17 +17716,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -17734,38 +17734,38 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>-0.17%591</t>
+          <t>-1%198.5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>591</v>
+        <v>198.5</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>1.00%716,000</t>
+          <t>1.57%788,000</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K284" t="n">
-        <v>716000</v>
+        <v>788000</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -17777,17 +17777,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -17795,38 +17795,38 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>+2.2%1160</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>1160</v>
+        <v>1710</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>0.82%300,000</t>
+          <t>1.42%82,000</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K285" t="n">
-        <v>300000</v>
+        <v>82000</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -17838,17 +17838,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -17856,38 +17856,38 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>+9.84%530</t>
+          <t>+6.11%1215</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>+9.84%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>530</v>
+        <v>1215</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>0.47%373,000</t>
+          <t>1.29%113,000</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K286" t="n">
-        <v>373000</v>
+        <v>113000</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -17899,17 +17899,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -17917,34 +17917,34 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>+3.14%296</t>
+          <t>+0.65%77.9</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>+3.14%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>296</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>0.46%659,000</t>
+          <t>1.28%1,657,000</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K287" t="n">
-        <v>659000</v>
+        <v>1657000</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -17960,17 +17960,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -17978,38 +17978,38 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>+1.32%768</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H288" t="n">
-        <v>768</v>
+        <v>5595</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>0.45%250,000</t>
+          <t>1.24%23,000</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K288" t="n">
-        <v>250000</v>
+        <v>23000</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -18021,17 +18021,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -18039,38 +18039,38 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>+7.05%2960</t>
+          <t>+1.82%670</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>+7.05%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H289" t="n">
-        <v>2960</v>
+        <v>670</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>0.44%63,000</t>
+          <t>0.96%146,000</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K289" t="n">
-        <v>63000</v>
+        <v>146000</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -18082,17 +18082,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -18100,38 +18100,38 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>+0.22%925</t>
+          <t>+1.8%510</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>925</v>
+        <v>510</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>0.43%196,000</t>
+          <t>0.96%193,000</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K290" t="n">
-        <v>196000</v>
+        <v>193000</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -18143,17 +18143,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -18161,38 +18161,38 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>+1.91%347.5</t>
+          <t>+2.43%971</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>347.5</v>
+        <v>971</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>0.42%508,000</t>
+          <t>0.93%98,000</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K291" t="n">
-        <v>508000</v>
+        <v>98000</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -18204,17 +18204,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -18222,38 +18222,38 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>+0.97%5205</t>
+          <t>+5.39%1270</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H292" t="n">
-        <v>5205</v>
+        <v>1270</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>0.41%33,000</t>
+          <t>0.67%56,000</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K292" t="n">
-        <v>33000</v>
+        <v>56000</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -18265,17 +18265,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -18283,38 +18283,38 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>-0.23%87.5</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>87.5</v>
+        <v>5720</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>0.40%1,957,000</t>
+          <t>0.64%12,000</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K293" t="n">
-        <v>1957000</v>
+        <v>12000</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -18326,17 +18326,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -18344,38 +18344,38 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>+5.39%1270</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>1270</v>
+        <v>1160</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>0.40%134,000</t>
+          <t>0.54%48,000</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K294" t="n">
-        <v>134000</v>
+        <v>48000</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -18387,17 +18387,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -18405,38 +18405,38 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>+1.89%15400</t>
+          <t>-1.27%544</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>+1.89%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>15400</v>
+        <v>544</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>0.40%11,000</t>
+          <t>0.49%89,000</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K295" t="n">
-        <v>11000</v>
+        <v>89000</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -18448,17 +18448,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -18466,34 +18466,34 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>+2.06%1485</t>
+          <t>+1.95%444</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>+2.06%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>1485</v>
+        <v>444</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>0.40%113,000</t>
+          <t>0.48%110,000</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K296" t="n">
-        <v>113000</v>
+        <v>110000</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -18509,17 +18509,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -18527,38 +18527,38 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>+0.47%1070</t>
+          <t>-2.34%2085</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>1070</v>
+        <v>2085</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>0.39%155,000</t>
+          <t>0.43%20,000</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K297" t="n">
-        <v>155000</v>
+        <v>20000</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -18570,17 +18570,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -18588,38 +18588,38 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>-2.33%628</t>
+          <t>+1.13%179</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>628</v>
+        <v>179</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>0.39%261,000</t>
+          <t>0.43%243,000</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K298" t="n">
-        <v>261000</v>
+        <v>243000</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -18631,17 +18631,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -18649,38 +18649,38 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3131弘塑科技</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>-5.07%1965</t>
+          <t>-3.21%2260</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>-5.07%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>1965</v>
+        <v>2260</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>0.35%76,000</t>
+          <t>0.28%12,000</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K299" t="n">
-        <v>76000</v>
+        <v>12000</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -18692,17 +18692,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -18710,38 +18710,38 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>-3.82%1510</t>
+          <t>+1.21%125</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>1510</v>
+        <v>125</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>0.35%98,000</t>
+          <t>0.21%171,000</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K300" t="n">
-        <v>98000</v>
+        <v>171000</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -18753,17 +18753,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -18771,38 +18771,38 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>1802台灣玻璃工業</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>-0.33%150.5</t>
+          <t>+1.93%58</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>150.5</v>
+        <v>58</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>0.22%629,000</t>
+          <t>0.20%357,000</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K301" t="n">
-        <v>629000</v>
+        <v>357000</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -18814,58 +18814,56 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
+          <t>2881富邦金融控股</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.2%141.5</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>141.5</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>3.54%935,600</t>
+          <t>0.20%154,000</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K302" t="n">
-        <v>935600</v>
+        <v>154000</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -18877,58 +18875,56 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>009150SAMSUNG ELECTRO-MECHANICS CO</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.42%64.5</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.42%</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>64.5</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>3.39%42,083</t>
+          <t>0.19%306,000</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K303" t="n">
-        <v>42083</v>
+        <v>306000</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -18940,58 +18936,56 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2049上銀科技</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>+1.86%1095</t>
+          <t>+0.58%345.5</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>+1.86%</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>1095</t>
-        </is>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>345.5</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>3.30%1,146,000</t>
+          <t>0.19%55,000</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K304" t="n">
-        <v>1146000</v>
+        <v>55000</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -19003,58 +18997,56 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>+3.04%5595</t>
+          <t>-0.23%2195</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>+3.04%</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>5595</t>
-        </is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>2195</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>3.20%212,000</t>
+          <t>0.18%8,000</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K305" t="n">
-        <v>212000</v>
+        <v>8000</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -19066,58 +19058,56 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>+1.05%2400</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>+1.05%</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>2075</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>2.60%406,000</t>
+          <t>0.18%9,000</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K306" t="n">
-        <v>406000</v>
+        <v>9000</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -19129,58 +19119,56 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>000660SK HYNIX INC</t>
+          <t>2317鴻海精密工業</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.21%243</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>243</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>2.23%21,113</t>
+          <t>0.16%64,000</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K307" t="n">
-        <v>21113</v>
+        <v>64000</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -19192,58 +19180,56 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>-1.44%1710</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>-1.44%</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+          <t>-5.07%</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>1965</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>2.05%441,000</t>
+          <t>0.10%5,000</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K308" t="n">
-        <v>441000</v>
+        <v>5000</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -19255,58 +19241,56 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>6857ADVANTEST CORP</t>
+          <t>6488環球晶圓</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.97%980</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.97%</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>980</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>1.69%88,100</t>
+          <t>0.10%10,000</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K309" t="n">
-        <v>88100</v>
+        <v>10000</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -19318,58 +19302,56 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>+2.06%1485</t>
+          <t>+5.16%835</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>+2.06%</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
+          <t>+5.16%</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>835</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>1.49%376,000</t>
+          <t>0.02%2,000</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K310" t="n">
-        <v>376000</v>
+        <v>2000</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -19381,58 +19363,56 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>-0.8%3735</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>14285</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>1.43%142,000</t>
+          <t>8.77%260,000</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="K311" t="n">
-        <v>142000</v>
+        <v>260000</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -19444,58 +19424,56 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>+0.63%5600</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
+          <t>+1.05%</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>2400</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>1.31%90,000</t>
+          <t>7.40%1,306,000</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>7.40%</t>
         </is>
       </c>
       <c r="K312" t="n">
-        <v>90000</v>
+        <v>1306000</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -19507,58 +19485,56 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>-0.17%591</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+          <t>+3.33%</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>2950</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>1.00%641,000</t>
+          <t>6.97%1,001,000</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="K313" t="n">
-        <v>641000</v>
+        <v>1001000</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -19570,58 +19546,56 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>-1.93%2030</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>-1.93%</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
+          <t>+1.86%</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>1095</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>0.93%172,000</t>
+          <t>6.42%2,482,000</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>6.42%</t>
         </is>
       </c>
       <c r="K314" t="n">
-        <v>172000</v>
+        <v>2482000</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -19633,58 +19607,56 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.04%</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>5595</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>0.92%89,700</t>
+          <t>6.14%465,000</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="K315" t="n">
-        <v>89700</v>
+        <v>465000</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -19696,58 +19668,56 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>+2.2%1160</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>+2.2%</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>2075</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>0.91%302,000</t>
+          <t>5.69%1,161,000</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>5.69%</t>
         </is>
       </c>
       <c r="K316" t="n">
-        <v>302000</v>
+        <v>1161000</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -19759,61 +19729,3141 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-1.93%2030</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-1.93%</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>2030</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>5.15%1,074,000</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>5.15%</t>
+        </is>
+      </c>
+      <c r="K317" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>8996高力</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>+6.11%1215</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>+6.11%</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>1215</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>4.67%1,630,000</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>4.67%</t>
+        </is>
+      </c>
+      <c r="K318" t="n">
+        <v>1630000</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>+6.22%5720</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>+6.22%</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>5720</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>4.63%343,000</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>4.63%</t>
+        </is>
+      </c>
+      <c r="K319" t="n">
+        <v>343000</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>+0.63%5600</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>3.54%268,000</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="K320" t="n">
+        <v>268000</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>6584南俊國際</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>+1.37%594</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>+1.37%</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>594</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>3.13%2,231,000</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="K321" t="n">
+        <v>2231000</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>3231緯創</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>+1.71%178.5</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>+1.71%</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>3.05%7,245,000</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="K322" t="n">
+        <v>7245000</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>1</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>1815富喬</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>+1.4%109</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>109</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>2.80%10,877,000</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>2.80%</t>
+        </is>
+      </c>
+      <c r="K323" t="n">
+        <v>10877000</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2455全新</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>+9.96%419.5</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>+9.96%</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>2.73%2,753,000</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="K324" t="n">
+        <v>2753000</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:10</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>8021尖點</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>+3.99%404</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>+3.99%</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>404</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>2.56%2,682,000</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="K325" t="n">
+        <v>2682000</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>2</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-1.44%1710</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>1710</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>2.55%632,000</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="K326" t="n">
+        <v>632000</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>2</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>1303南亞</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>+4.72%188.5</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>+4.72%</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>2.42%5,445,000</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="K327" t="n">
+        <v>5445000</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>2</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-0.8%3735</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>3735</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>2.35%266,000</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
+      </c>
+      <c r="K328" t="n">
+        <v>266000</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>2</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>3443創意</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>+3.82%5570</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>+3.82%</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>5570</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>2.16%164,000</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="K329" t="n">
+        <v>164000</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>2</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>3661世芯-KY</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>+3.48%3865</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>+3.48%</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>3865</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>1.96%215,000</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="K330" t="n">
+        <v>215000</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>2</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>3189景碩</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>+5.16%835</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>+5.16%</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>835</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>1.66%844,013</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="K331" t="n">
+        <v>844013</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>2</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>6669緯穎</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>+2.22%6440</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>+2.22%</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>6440</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>1.17%77,000</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="K332" t="n">
+        <v>77000</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>2</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>4958臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>+1.95%444</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>+1.95%</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>444</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>1.05%1,000,000</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="K333" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>2</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-0.17%591</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>591</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>1.00%716,000</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="K334" t="n">
+        <v>716000</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>2</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>8046南電</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>+2.2%1160</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>1160</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>0.82%300,000</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="K335" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>2</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>6213聯茂</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>+9.84%530</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>+9.84%</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>530</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>0.47%373,000</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="K336" t="n">
+        <v>373000</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>2</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2301光寶科</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>+3.14%296</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>+3.14%</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>296</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>0.46%659,000</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="K337" t="n">
+        <v>659000</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>2</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>6139亞翔</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>+1.32%768</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>+1.32%</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>768</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>0.45%250,000</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="K338" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>2</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>3081聯亞</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>+7.05%2960</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>+7.05%</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>2960</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>0.44%63,000</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="K339" t="n">
+        <v>63000</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:11</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>2</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2357華碩</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>+0.22%925</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>925</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>0.43%196,000</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="K340" t="n">
+        <v>196000</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>3</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2376技嘉</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>+1.91%347.5</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>+1.91%</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>0.42%508,000</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="K341" t="n">
+        <v>508000</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>3</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>3653健策</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>+0.97%5205</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>5205</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>0.41%33,000</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="K342" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>3</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>8150南茂</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-0.23%87.5</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>0.40%1,957,000</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K343" t="n">
+        <v>1957000</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>3</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>6187萬潤</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>+5.39%1270</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>+5.39%</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>1270</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>0.40%134,000</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K344" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>3</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>5274信驊</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>+1.89%15400</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>+1.89%</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>15400</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>0.40%11,000</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K345" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>3</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>+2.06%1485</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>+2.06%</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>1485</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>0.40%113,000</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K346" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>3</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2404漢唐</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>+0.47%1070</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>+0.47%</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>1070</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>0.39%155,000</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="K347" t="n">
+        <v>155000</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>3</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>3026禾伸堂</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-2.33%628</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-2.33%</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>628</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>0.39%261,000</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="K348" t="n">
+        <v>261000</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>3</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-5.07%1965</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-5.07%</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>1965</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>0.35%76,000</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="K349" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>3</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>5289宜鼎</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-3.82%1510</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-3.82%</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>1510</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>0.35%98,000</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="K350" t="n">
+        <v>98000</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:12</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>3</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>5347世界</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-0.33%150.5</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>0.22%629,000</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="K351" t="n">
+        <v>629000</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
           <t>00990A</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-08-25 19:52:48</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:18</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
         <is>
           <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
-      <c r="D317" t="n">
+      <c r="D352" t="n">
+        <v>1</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>3.54%935,600</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="K352" t="n">
+        <v>935600</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:18</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>009150SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>3.39%42,083</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="K353" t="n">
+        <v>42083</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:18</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>3037欣興</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>+1.86%1095</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>+1.86%</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>3.30%1,146,000</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="K354" t="n">
+        <v>1146000</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:18</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2383台光電</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>+3.04%5595</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>+3.04%</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>3.20%212,000</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>3.20%</t>
+        </is>
+      </c>
+      <c r="K355" t="n">
+        <v>212000</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:18</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2330台積電</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>+1.05%2400</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>+1.05%</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>2.60%406,000</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="K356" t="n">
+        <v>406000</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:18</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>1</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>000660SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>2.23%21,113</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="K357" t="n">
+        <v>21113</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:20</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>2</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-1.44%1710</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2.05%441,000</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="K358" t="n">
+        <v>441000</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:20</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>2</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>6857ADVANTEST CORP</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>1.69%88,100</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="K359" t="n">
+        <v>88100</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:20</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>2</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>+2.06%1485</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>+2.06%</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>1.49%376,000</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="K360" t="n">
+        <v>376000</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:20</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>2</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-0.8%3735</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>1.43%142,000</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="K361" t="n">
+        <v>142000</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:21</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
         <v>3</v>
       </c>
-      <c r="E317" t="inlineStr">
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>+0.63%5600</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>1.31%90,000</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="K362" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:21</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>3</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-0.17%591</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>1.00%641,000</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="K363" t="n">
+        <v>641000</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:21</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>3</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-1.93%2030</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-1.93%</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>0.93%172,000</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="K364" t="n">
+        <v>172000</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:21</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>3</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>4062IBIDEN CO LTD</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>0.92%89,700</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="K365" t="n">
+        <v>89700</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:21</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>3</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>8046南電</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>+2.2%1160</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>0.91%302,000</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="K366" t="n">
+        <v>302000</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:10:21</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>3</v>
+      </c>
+      <c r="E367" t="inlineStr">
         <is>
           <t>2449京元電子</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
+      <c r="F367" t="inlineStr">
         <is>
           <t>+0.21%239.5</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
+      <c r="G367" t="inlineStr">
         <is>
           <t>+0.21%</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
+      <c r="H367" t="inlineStr">
         <is>
           <t>239.5</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr">
+      <c r="I367" t="inlineStr">
         <is>
           <t>0.62%1,008,000</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr">
+      <c r="J367" t="inlineStr">
         <is>
           <t>0.62%</t>
         </is>
       </c>
-      <c r="K317" t="n">
+      <c r="K367" t="n">
         <v>1008000</v>
       </c>
-      <c r="L317" t="inlineStr">
+      <c r="L367" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
+      <c r="M367" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M367"/>
+  <dimension ref="A1:M317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:30</t>
+          <t>2026-08-25 21:28:04</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:31</t>
+          <t>2026-08-25 21:28:06</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:32</t>
+          <t>2026-08-25 21:28:07</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:34</t>
+          <t>2026-08-25 21:28:08</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:34</t>
+          <t>2026-08-25 21:28:08</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:34</t>
+          <t>2026-08-25 21:28:08</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:34</t>
+          <t>2026-08-25 21:28:08</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:34</t>
+          <t>2026-08-25 21:28:08</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:51</t>
+          <t>2026-08-25 21:28:24</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:52</t>
+          <t>2026-08-25 21:28:26</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:53</t>
+          <t>2026-08-25 21:28:27</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:55</t>
+          <t>2026-08-25 21:28:28</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:55</t>
+          <t>2026-08-25 21:28:28</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:55</t>
+          <t>2026-08-25 21:28:28</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:55</t>
+          <t>2026-08-25 21:28:28</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:55</t>
+          <t>2026-08-25 21:28:28</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16313,17 +16313,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -16331,38 +16331,38 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2330台灣積體電路製造</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>+1.05%2400</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2400</v>
+        <v>14285</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>13.92%588,000</t>
+          <t>8.77%260,000</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>13.92%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="K261" t="n">
-        <v>588000</v>
+        <v>260000</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -16374,17 +16374,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -16392,38 +16392,38 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2376技嘉科技</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>+1.91%347.5</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>347.5</v>
+        <v>2400</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>4.92%1,448,000</t>
+          <t>7.40%1,306,000</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>4.92%</t>
+          <t>7.40%</t>
         </is>
       </c>
       <c r="K262" t="n">
-        <v>1448000</v>
+        <v>1306000</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -16435,17 +16435,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -16453,38 +16453,38 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>-1.8%246</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>246</v>
+        <v>2950</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>4.34%1,737,000</t>
+          <t>6.97%1,001,000</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="K263" t="n">
-        <v>1737000</v>
+        <v>1001000</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -16496,17 +16496,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -16514,38 +16514,38 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>4904遠傳電信</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>+0.99%102.5</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>102.5</v>
+        <v>1095</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>3.88%3,832,000</t>
+          <t>6.42%2,482,000</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>6.42%</t>
         </is>
       </c>
       <c r="K264" t="n">
-        <v>3832000</v>
+        <v>2482000</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -16557,17 +16557,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -16575,38 +16575,38 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2412中華電信</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>0%136.5</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>136.5</v>
+        <v>5595</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>3.85%2,828,000</t>
+          <t>6.14%465,000</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="K265" t="n">
-        <v>2828000</v>
+        <v>465000</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -16618,17 +16618,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -16636,34 +16636,34 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>6669緯穎科技服務</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>+2.22%6440</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>6440</v>
+        <v>2075</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>3.33%53,000</t>
+          <t>5.69%1,161,000</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>5.69%</t>
         </is>
       </c>
       <c r="K266" t="n">
-        <v>53000</v>
+        <v>1161000</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -16679,17 +16679,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -16715,20 +16715,20 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2.56%124,000</t>
+          <t>5.15%1,074,000</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>5.15%</t>
         </is>
       </c>
       <c r="K267" t="n">
-        <v>124000</v>
+        <v>1074000</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -16740,17 +16740,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -16758,38 +16758,38 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>+0.97%5205</t>
+          <t>+6.11%1215</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>5205</v>
+        <v>1215</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2.52%49,000</t>
+          <t>4.67%1,630,000</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>4.67%</t>
         </is>
       </c>
       <c r="K268" t="n">
-        <v>49000</v>
+        <v>1630000</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -16801,17 +16801,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -16819,38 +16819,38 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>1504東元電機</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>-0.98%70.8</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>70.8</v>
+        <v>5720</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2.47%3,473,000</t>
+          <t>4.63%343,000</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="K269" t="n">
-        <v>3473000</v>
+        <v>343000</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -16862,17 +16862,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -16880,38 +16880,38 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>3105穩懋半導體</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>+6.76%379</t>
+          <t>+0.63%5600</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>+6.76%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>379</v>
+        <v>5600</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2.32%656,000</t>
+          <t>3.54%268,000</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K270" t="n">
-        <v>656000</v>
+        <v>268000</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -16923,17 +16923,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -16941,38 +16941,38 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>7750新代科技</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>+9.81%2350</t>
+          <t>+1.37%594</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>+9.81%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H271" t="n">
-        <v>2350</v>
+        <v>594</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2.30%108,000</t>
+          <t>3.13%2,231,000</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K271" t="n">
-        <v>108000</v>
+        <v>2231000</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -16984,17 +16984,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -17002,38 +17002,38 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>3081聯亞光電工業</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>+7.05%2960</t>
+          <t>+1.71%178.5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>+7.05%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>2960</v>
+        <v>178.5</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2.29%83,000</t>
+          <t>3.05%7,245,000</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K272" t="n">
-        <v>83000</v>
+        <v>7245000</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -17045,17 +17045,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -17063,38 +17063,38 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>+9.93%1605</t>
+          <t>+1.4%109</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H273" t="n">
-        <v>1605</v>
+        <v>109</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2.15%148,000</t>
+          <t>2.80%10,877,000</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="K273" t="n">
-        <v>148000</v>
+        <v>10877000</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -17106,17 +17106,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -17124,38 +17124,38 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2027大成不銹鋼工業</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>-0.78%50.6</t>
+          <t>+9.96%419.5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H274" t="n">
-        <v>50.6</v>
+        <v>419.5</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2.13%4,181,000</t>
+          <t>2.73%2,753,000</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K274" t="n">
-        <v>4181000</v>
+        <v>2753000</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -17167,17 +17167,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -17185,38 +17185,38 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>-0.17%591</t>
+          <t>+3.99%404</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>591</v>
+        <v>404</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>1.98%335,000</t>
+          <t>2.56%2,682,000</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K275" t="n">
-        <v>335000</v>
+        <v>2682000</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -17228,17 +17228,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -17246,38 +17246,38 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>-0.72%6210</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>6210</v>
+        <v>1710</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>1.93%31,000</t>
+          <t>2.55%632,000</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="K276" t="n">
-        <v>31000</v>
+        <v>632000</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -17289,17 +17289,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -17307,38 +17307,38 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>+3.33%2950</t>
+          <t>+4.72%188.5</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>+4.72%</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>2950</v>
+        <v>188.5</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>1.93%68,000</t>
+          <t>2.42%5,445,000</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K277" t="n">
-        <v>68000</v>
+        <v>5445000</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -17350,17 +17350,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17386,16 +17386,16 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>1.88%50,000</t>
+          <t>2.35%266,000</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K278" t="n">
-        <v>50000</v>
+        <v>266000</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -17411,17 +17411,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -17429,38 +17429,38 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2610中華航空</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>-0.49%20.4</t>
+          <t>+3.82%5570</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+3.82%</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>20.4</v>
+        <v>5570</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>1.79%8,783,000</t>
+          <t>2.16%164,000</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K279" t="n">
-        <v>8783000</v>
+        <v>164000</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -17472,17 +17472,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -17490,38 +17490,38 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>3037欣興電子</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>+1.86%1095</t>
+          <t>+3.48%3865</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>+3.48%</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1095</v>
+        <v>3865</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>1.71%160,000</t>
+          <t>1.96%215,000</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K280" t="n">
-        <v>160000</v>
+        <v>215000</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -17533,17 +17533,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -17551,38 +17551,38 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>+1.02%1490</t>
+          <t>+5.16%835</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>+5.16%</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>1490</v>
+        <v>835</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>1.59%108,000</t>
+          <t>1.66%844,013</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K281" t="n">
-        <v>108000</v>
+        <v>844013</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -17594,17 +17594,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -17612,38 +17612,38 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>6147頎邦科技</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>+7.64%169</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>+7.64%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>169</v>
+        <v>6440</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>1.59%1,019,000</t>
+          <t>1.17%77,000</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K282" t="n">
-        <v>1019000</v>
+        <v>77000</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -17655,17 +17655,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -17673,38 +17673,38 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>-0.87%14285</t>
+          <t>+1.95%444</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>14285</v>
+        <v>444</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>1.58%11,000</t>
+          <t>1.05%1,000,000</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K283" t="n">
-        <v>11000</v>
+        <v>1000000</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -17716,17 +17716,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -17734,38 +17734,38 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>-1%198.5</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>198.5</v>
+        <v>591</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>1.57%788,000</t>
+          <t>1.00%716,000</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K284" t="n">
-        <v>788000</v>
+        <v>716000</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -17777,17 +17777,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -17795,38 +17795,38 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2308台達電子工業</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>-1.44%1710</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>1710</v>
+        <v>1160</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>1.42%82,000</t>
+          <t>0.82%300,000</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K285" t="n">
-        <v>82000</v>
+        <v>300000</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -17838,17 +17838,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -17856,38 +17856,38 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>+6.11%1215</t>
+          <t>+9.84%530</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+9.84%</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>1215</v>
+        <v>530</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>1.29%113,000</t>
+          <t>0.47%373,000</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K286" t="n">
-        <v>113000</v>
+        <v>373000</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -17899,17 +17899,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -17917,34 +17917,34 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>+0.65%77.9</t>
+          <t>+3.14%296</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+3.14%</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>77.90000000000001</v>
+        <v>296</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>1.28%1,657,000</t>
+          <t>0.46%659,000</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K287" t="n">
-        <v>1657000</v>
+        <v>659000</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -17960,17 +17960,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -17978,38 +17978,38 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2383台光電子材料</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>+3.04%5595</t>
+          <t>+1.32%768</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>+3.04%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H288" t="n">
-        <v>5595</v>
+        <v>768</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>1.24%23,000</t>
+          <t>0.45%250,000</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K288" t="n">
-        <v>23000</v>
+        <v>250000</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -18021,17 +18021,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -18039,38 +18039,38 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>+1.82%670</t>
+          <t>+7.05%2960</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>+7.05%</t>
         </is>
       </c>
       <c r="H289" t="n">
-        <v>670</v>
+        <v>2960</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>0.96%146,000</t>
+          <t>0.44%63,000</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K289" t="n">
-        <v>146000</v>
+        <v>63000</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -18082,17 +18082,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -18100,38 +18100,38 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>+1.8%510</t>
+          <t>+0.22%925</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>510</v>
+        <v>925</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>0.96%193,000</t>
+          <t>0.43%196,000</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K290" t="n">
-        <v>193000</v>
+        <v>196000</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -18143,17 +18143,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -18161,38 +18161,38 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>+2.43%971</t>
+          <t>+1.91%347.5</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>+2.43%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>971</v>
+        <v>347.5</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>0.93%98,000</t>
+          <t>0.42%508,000</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K291" t="n">
-        <v>98000</v>
+        <v>508000</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -18204,17 +18204,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -18222,38 +18222,38 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>+5.39%1270</t>
+          <t>+0.97%5205</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H292" t="n">
-        <v>1270</v>
+        <v>5205</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>0.67%56,000</t>
+          <t>0.41%33,000</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K292" t="n">
-        <v>56000</v>
+        <v>33000</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -18265,17 +18265,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -18283,38 +18283,38 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>+6.22%5720</t>
+          <t>-0.23%87.5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>+6.22%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>5720</v>
+        <v>87.5</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>0.64%12,000</t>
+          <t>0.40%1,957,000</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K293" t="n">
-        <v>12000</v>
+        <v>1957000</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -18326,17 +18326,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -18344,38 +18344,38 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>+2.2%1160</t>
+          <t>+5.39%1270</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>1160</v>
+        <v>1270</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>0.54%48,000</t>
+          <t>0.40%134,000</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K294" t="n">
-        <v>48000</v>
+        <v>134000</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -18387,17 +18387,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -18405,38 +18405,38 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>-1.27%544</t>
+          <t>+1.89%15400</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>544</v>
+        <v>15400</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>0.49%89,000</t>
+          <t>0.40%11,000</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K295" t="n">
-        <v>89000</v>
+        <v>11000</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -18448,17 +18448,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -18466,34 +18466,34 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>4958臻鼎科技控股</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>+1.95%444</t>
+          <t>+2.06%1485</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>444</v>
+        <v>1485</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>0.48%110,000</t>
+          <t>0.40%113,000</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K296" t="n">
-        <v>110000</v>
+        <v>113000</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -18509,17 +18509,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -18527,38 +18527,38 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>-2.34%2085</t>
+          <t>+0.47%1070</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>2085</v>
+        <v>1070</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>0.43%20,000</t>
+          <t>0.39%155,000</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K297" t="n">
-        <v>20000</v>
+        <v>155000</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -18570,17 +18570,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -18588,38 +18588,38 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>+1.13%179</t>
+          <t>-2.33%628</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>179</v>
+        <v>628</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>0.43%243,000</t>
+          <t>0.39%261,000</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K298" t="n">
-        <v>243000</v>
+        <v>261000</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -18631,17 +18631,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -18649,38 +18649,38 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>3131弘塑科技</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>-3.21%2260</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>2260</v>
+        <v>1965</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>0.28%12,000</t>
+          <t>0.35%76,000</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K299" t="n">
-        <v>12000</v>
+        <v>76000</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -18692,17 +18692,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -18710,38 +18710,38 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>+1.21%125</t>
+          <t>-3.82%1510</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>125</v>
+        <v>1510</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>0.21%171,000</t>
+          <t>0.35%98,000</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K300" t="n">
-        <v>171000</v>
+        <v>98000</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -18753,17 +18753,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -18771,38 +18771,38 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>1802台灣玻璃工業</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>+1.93%58</t>
+          <t>-0.33%150.5</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>58</v>
+        <v>150.5</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>0.20%357,000</t>
+          <t>0.22%629,000</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K301" t="n">
-        <v>357000</v>
+        <v>629000</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -18814,56 +18814,58 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2881富邦金融控股</t>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>+7.2%141.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>+7.2%</t>
-        </is>
-      </c>
-      <c r="H302" t="n">
-        <v>141.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>0.20%154,000</t>
+          <t>3.54%935,600</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K302" t="n">
-        <v>154000</v>
+        <v>935600</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -18875,56 +18877,58 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>009150SAMSUNG ELECTRO-MECHANICS CO</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>+1.42%64.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>+1.42%</t>
-        </is>
-      </c>
-      <c r="H303" t="n">
-        <v>64.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>0.19%306,000</t>
+          <t>3.39%42,083</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="K303" t="n">
-        <v>306000</v>
+        <v>42083</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -18936,56 +18940,58 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2049上銀科技</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>+0.58%345.5</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>+0.58%</t>
-        </is>
-      </c>
-      <c r="H304" t="n">
-        <v>345.5</v>
+          <t>+1.86%</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>0.19%55,000</t>
+          <t>3.30%1,146,000</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K304" t="n">
-        <v>55000</v>
+        <v>1146000</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -18997,56 +19003,58 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>-0.23%2195</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="H305" t="n">
-        <v>2195</v>
+          <t>+3.04%</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>0.18%8,000</t>
+          <t>3.20%212,000</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K305" t="n">
-        <v>8000</v>
+        <v>212000</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -19058,56 +19066,58 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>+1.22%2075</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>+1.22%</t>
-        </is>
-      </c>
-      <c r="H306" t="n">
-        <v>2075</v>
+          <t>+1.05%</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>0.18%9,000</t>
+          <t>2.60%406,000</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="K306" t="n">
-        <v>9000</v>
+        <v>406000</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -19119,56 +19129,58 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2317鴻海精密工業</t>
+          <t>000660SK HYNIX INC</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>-0.21%243</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="H307" t="n">
-        <v>243</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>0.16%64,000</t>
+          <t>2.23%21,113</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K307" t="n">
-        <v>64000</v>
+        <v>21113</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -19180,56 +19192,58 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>-5.07%1965</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>-5.07%</t>
-        </is>
-      </c>
-      <c r="H308" t="n">
-        <v>1965</v>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>0.10%5,000</t>
+          <t>2.05%441,000</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K308" t="n">
-        <v>5000</v>
+        <v>441000</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -19241,56 +19255,58 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>6488環球晶圓</t>
+          <t>6857ADVANTEST CORP</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>-2.97%980</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>-2.97%</t>
-        </is>
-      </c>
-      <c r="H309" t="n">
-        <v>980</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>0.10%10,000</t>
+          <t>1.69%88,100</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K309" t="n">
-        <v>10000</v>
+        <v>88100</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -19302,56 +19318,58 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>+5.16%835</t>
+          <t>+2.06%1485</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>+5.16%</t>
-        </is>
-      </c>
-      <c r="H310" t="n">
-        <v>835</v>
+          <t>+2.06%</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>0.02%2,000</t>
+          <t>1.49%376,000</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K310" t="n">
-        <v>2000</v>
+        <v>376000</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -19363,56 +19381,58 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>-0.87%14285</t>
+          <t>-0.8%3735</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>-0.87%</t>
-        </is>
-      </c>
-      <c r="H311" t="n">
-        <v>14285</v>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>8.77%260,000</t>
+          <t>1.43%142,000</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K311" t="n">
-        <v>260000</v>
+        <v>142000</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -19424,56 +19444,58 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>+1.05%2400</t>
+          <t>+0.63%5600</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>+1.05%</t>
-        </is>
-      </c>
-      <c r="H312" t="n">
-        <v>2400</v>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>7.40%1,306,000</t>
+          <t>1.31%90,000</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K312" t="n">
-        <v>1306000</v>
+        <v>90000</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -19485,56 +19507,58 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>+3.33%2950</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>+3.33%</t>
-        </is>
-      </c>
-      <c r="H313" t="n">
-        <v>2950</v>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>6.97%1,001,000</t>
+          <t>1.00%641,000</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K313" t="n">
-        <v>1001000</v>
+        <v>641000</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -19546,56 +19570,58 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>+1.86%1095</t>
+          <t>-1.93%2030</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>+1.86%</t>
-        </is>
-      </c>
-      <c r="H314" t="n">
-        <v>1095</v>
+          <t>-1.93%</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>6.42%2,482,000</t>
+          <t>0.93%172,000</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K314" t="n">
-        <v>2482000</v>
+        <v>172000</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -19607,56 +19633,58 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>4062IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>+3.04%5595</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>+3.04%</t>
-        </is>
-      </c>
-      <c r="H315" t="n">
-        <v>5595</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>6.14%465,000</t>
+          <t>0.92%89,700</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K315" t="n">
-        <v>465000</v>
+        <v>89700</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -19668,56 +19696,58 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>+1.22%2075</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>+1.22%</t>
-        </is>
-      </c>
-      <c r="H316" t="n">
-        <v>2075</v>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>5.69%1,161,000</t>
+          <t>0.91%302,000</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K316" t="n">
-        <v>1161000</v>
+        <v>302000</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -19729,3141 +19759,61 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>-1.93%2030</t>
+          <t>+0.21%239.5</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>-1.93%</t>
-        </is>
-      </c>
-      <c r="H317" t="n">
-        <v>2030</v>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>239.5</t>
+        </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>5.15%1,074,000</t>
+          <t>0.62%1,008,000</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K317" t="n">
-        <v>1074000</v>
+        <v>1008000</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D318" t="n">
-        <v>1</v>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>8996高力</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>+6.11%1215</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>+6.11%</t>
-        </is>
-      </c>
-      <c r="H318" t="n">
-        <v>1215</v>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>4.67%1,630,000</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>4.67%</t>
-        </is>
-      </c>
-      <c r="K318" t="n">
-        <v>1630000</v>
-      </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>+0.27%</t>
-        </is>
-      </c>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D319" t="n">
-        <v>1</v>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>3008大立光</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>+6.22%5720</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>+6.22%</t>
-        </is>
-      </c>
-      <c r="H319" t="n">
-        <v>5720</v>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>4.63%343,000</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>4.63%</t>
-        </is>
-      </c>
-      <c r="K319" t="n">
-        <v>343000</v>
-      </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t>+0.28%</t>
-        </is>
-      </c>
-      <c r="M319" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D320" t="n">
-        <v>1</v>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>6223旺矽</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>+0.63%5600</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="H320" t="n">
-        <v>5600</v>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>3.54%268,000</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>3.54%</t>
-        </is>
-      </c>
-      <c r="K320" t="n">
-        <v>268000</v>
-      </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D321" t="n">
-        <v>1</v>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>6584南俊國際</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>+1.37%594</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>+1.37%</t>
-        </is>
-      </c>
-      <c r="H321" t="n">
-        <v>594</v>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>3.13%2,231,000</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="K321" t="n">
-        <v>2231000</v>
-      </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D322" t="n">
-        <v>1</v>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>3231緯創</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>+1.71%178.5</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>+1.71%</t>
-        </is>
-      </c>
-      <c r="H322" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>3.05%7,245,000</t>
-        </is>
-      </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>3.05%</t>
-        </is>
-      </c>
-      <c r="K322" t="n">
-        <v>7245000</v>
-      </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D323" t="n">
-        <v>1</v>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>1815富喬</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>+1.4%109</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>+1.4%</t>
-        </is>
-      </c>
-      <c r="H323" t="n">
-        <v>109</v>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>2.80%10,877,000</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>2.80%</t>
-        </is>
-      </c>
-      <c r="K323" t="n">
-        <v>10877000</v>
-      </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D324" t="n">
-        <v>1</v>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>2455全新</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>+9.96%419.5</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>+9.96%</t>
-        </is>
-      </c>
-      <c r="H324" t="n">
-        <v>419.5</v>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>2.73%2,753,000</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>2.73%</t>
-        </is>
-      </c>
-      <c r="K324" t="n">
-        <v>2753000</v>
-      </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>+0.25%</t>
-        </is>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:10</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D325" t="n">
-        <v>1</v>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>8021尖點</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>+3.99%404</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>+3.99%</t>
-        </is>
-      </c>
-      <c r="H325" t="n">
-        <v>404</v>
-      </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>2.56%2,682,000</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>2.56%</t>
-        </is>
-      </c>
-      <c r="K325" t="n">
-        <v>2682000</v>
-      </c>
-      <c r="L325" t="inlineStr">
-        <is>
-          <t>+0.10%</t>
-        </is>
-      </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D326" t="n">
-        <v>2</v>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>2308台達電</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>-1.44%1710</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>-1.44%</t>
-        </is>
-      </c>
-      <c r="H326" t="n">
-        <v>1710</v>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>2.55%632,000</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>2.55%</t>
-        </is>
-      </c>
-      <c r="K326" t="n">
-        <v>632000</v>
-      </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D327" t="n">
-        <v>2</v>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>1303南亞</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>+4.72%188.5</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>+4.72%</t>
-        </is>
-      </c>
-      <c r="H327" t="n">
-        <v>188.5</v>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>2.42%5,445,000</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="K327" t="n">
-        <v>5445000</v>
-      </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D328" t="n">
-        <v>2</v>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>2454聯發科</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>-0.8%3735</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H328" t="n">
-        <v>3735</v>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>2.35%266,000</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>2.35%</t>
-        </is>
-      </c>
-      <c r="K328" t="n">
-        <v>266000</v>
-      </c>
-      <c r="L328" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D329" t="n">
-        <v>2</v>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>3443創意</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>+3.82%5570</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>+3.82%</t>
-        </is>
-      </c>
-      <c r="H329" t="n">
-        <v>5570</v>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>2.16%164,000</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>2.16%</t>
-        </is>
-      </c>
-      <c r="K329" t="n">
-        <v>164000</v>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D330" t="n">
-        <v>2</v>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>3661世芯-KY</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>+3.48%3865</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>+3.48%</t>
-        </is>
-      </c>
-      <c r="H330" t="n">
-        <v>3865</v>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>1.96%215,000</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>1.96%</t>
-        </is>
-      </c>
-      <c r="K330" t="n">
-        <v>215000</v>
-      </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D331" t="n">
-        <v>2</v>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>3189景碩</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>+5.16%835</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>+5.16%</t>
-        </is>
-      </c>
-      <c r="H331" t="n">
-        <v>835</v>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>1.66%844,013</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>1.66%</t>
-        </is>
-      </c>
-      <c r="K331" t="n">
-        <v>844013</v>
-      </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D332" t="n">
-        <v>2</v>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>6669緯穎</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>+2.22%6440</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>+2.22%</t>
-        </is>
-      </c>
-      <c r="H332" t="n">
-        <v>6440</v>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>1.17%77,000</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>1.17%</t>
-        </is>
-      </c>
-      <c r="K332" t="n">
-        <v>77000</v>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D333" t="n">
-        <v>2</v>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>4958臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>+1.95%444</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>+1.95%</t>
-        </is>
-      </c>
-      <c r="H333" t="n">
-        <v>444</v>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>1.05%1,000,000</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="K333" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D334" t="n">
-        <v>2</v>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>-0.17%591</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="H334" t="n">
-        <v>591</v>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>1.00%716,000</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="K334" t="n">
-        <v>716000</v>
-      </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D335" t="n">
-        <v>2</v>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>8046南電</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>+2.2%1160</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>+2.2%</t>
-        </is>
-      </c>
-      <c r="H335" t="n">
-        <v>1160</v>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>0.82%300,000</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="K335" t="n">
-        <v>300000</v>
-      </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D336" t="n">
-        <v>2</v>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>6213聯茂</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>+9.84%530</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>+9.84%</t>
-        </is>
-      </c>
-      <c r="H336" t="n">
-        <v>530</v>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>0.47%373,000</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>0.47%</t>
-        </is>
-      </c>
-      <c r="K336" t="n">
-        <v>373000</v>
-      </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D337" t="n">
-        <v>2</v>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>2301光寶科</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>+3.14%296</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>+3.14%</t>
-        </is>
-      </c>
-      <c r="H337" t="n">
-        <v>296</v>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>0.46%659,000</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="K337" t="n">
-        <v>659000</v>
-      </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D338" t="n">
-        <v>2</v>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>6139亞翔</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>+1.32%768</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>+1.32%</t>
-        </is>
-      </c>
-      <c r="H338" t="n">
-        <v>768</v>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>0.45%250,000</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="K338" t="n">
-        <v>250000</v>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D339" t="n">
-        <v>2</v>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>3081聯亞</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>+7.05%2960</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>+7.05%</t>
-        </is>
-      </c>
-      <c r="H339" t="n">
-        <v>2960</v>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>0.44%63,000</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="K339" t="n">
-        <v>63000</v>
-      </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:11</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D340" t="n">
-        <v>2</v>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>2357華碩</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>+0.22%925</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>+0.22%</t>
-        </is>
-      </c>
-      <c r="H340" t="n">
-        <v>925</v>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>0.43%196,000</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="K340" t="n">
-        <v>196000</v>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D341" t="n">
-        <v>3</v>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>2376技嘉</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>+1.91%347.5</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>+1.91%</t>
-        </is>
-      </c>
-      <c r="H341" t="n">
-        <v>347.5</v>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>0.42%508,000</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="K341" t="n">
-        <v>508000</v>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D342" t="n">
-        <v>3</v>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>3653健策</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>+0.97%5205</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>+0.97%</t>
-        </is>
-      </c>
-      <c r="H342" t="n">
-        <v>5205</v>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>0.41%33,000</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>0.41%</t>
-        </is>
-      </c>
-      <c r="K342" t="n">
-        <v>33000</v>
-      </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D343" t="n">
-        <v>3</v>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>8150南茂</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-0.23%87.5</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="H343" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>0.40%1,957,000</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="K343" t="n">
-        <v>1957000</v>
-      </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D344" t="n">
-        <v>3</v>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>6187萬潤</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>+5.39%1270</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>+5.39%</t>
-        </is>
-      </c>
-      <c r="H344" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>0.40%134,000</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="K344" t="n">
-        <v>134000</v>
-      </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D345" t="n">
-        <v>3</v>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>5274信驊</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>+1.89%15400</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>+1.89%</t>
-        </is>
-      </c>
-      <c r="H345" t="n">
-        <v>15400</v>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>0.40%11,000</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="K345" t="n">
-        <v>11000</v>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D346" t="n">
-        <v>3</v>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>6274台燿</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>+2.06%1485</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>+2.06%</t>
-        </is>
-      </c>
-      <c r="H346" t="n">
-        <v>1485</v>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>0.40%113,000</t>
-        </is>
-      </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="K346" t="n">
-        <v>113000</v>
-      </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D347" t="n">
-        <v>3</v>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>2404漢唐</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>+0.47%1070</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>+0.47%</t>
-        </is>
-      </c>
-      <c r="H347" t="n">
-        <v>1070</v>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>0.39%155,000</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="K347" t="n">
-        <v>155000</v>
-      </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D348" t="n">
-        <v>3</v>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>3026禾伸堂</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>-2.33%628</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>-2.33%</t>
-        </is>
-      </c>
-      <c r="H348" t="n">
-        <v>628</v>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>0.39%261,000</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="K348" t="n">
-        <v>261000</v>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D349" t="n">
-        <v>3</v>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>2360致茂</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>-5.07%1965</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>-5.07%</t>
-        </is>
-      </c>
-      <c r="H349" t="n">
-        <v>1965</v>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>0.35%76,000</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="K349" t="n">
-        <v>76000</v>
-      </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D350" t="n">
-        <v>3</v>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>5289宜鼎</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>-3.82%1510</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>-3.82%</t>
-        </is>
-      </c>
-      <c r="H350" t="n">
-        <v>1510</v>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>0.35%98,000</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="K350" t="n">
-        <v>98000</v>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:12</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D351" t="n">
-        <v>3</v>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>5347世界</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>-0.33%150.5</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
-        </is>
-      </c>
-      <c r="H351" t="n">
-        <v>150.5</v>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>0.22%629,000</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>0.22%</t>
-        </is>
-      </c>
-      <c r="K351" t="n">
-        <v>629000</v>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:18</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D352" t="n">
-        <v>1</v>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>3.54%935,600</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>3.54%</t>
-        </is>
-      </c>
-      <c r="K352" t="n">
-        <v>935600</v>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:18</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D353" t="n">
-        <v>1</v>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>009150SAMSUNG ELECTRO-MECHANICS CO</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>3.39%42,083</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>3.39%</t>
-        </is>
-      </c>
-      <c r="K353" t="n">
-        <v>42083</v>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:18</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D354" t="n">
-        <v>1</v>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>3037欣興</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>+1.86%1095</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>+1.86%</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>1095</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>3.30%1,146,000</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>3.30%</t>
-        </is>
-      </c>
-      <c r="K354" t="n">
-        <v>1146000</v>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:18</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D355" t="n">
-        <v>1</v>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>2383台光電</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>+3.04%5595</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>+3.04%</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>5595</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>3.20%212,000</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>3.20%</t>
-        </is>
-      </c>
-      <c r="K355" t="n">
-        <v>212000</v>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:18</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D356" t="n">
-        <v>1</v>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>2330台積電</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>+1.05%2400</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>+1.05%</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>2.60%406,000</t>
-        </is>
-      </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>2.60%</t>
-        </is>
-      </c>
-      <c r="K356" t="n">
-        <v>406000</v>
-      </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M356" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:18</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D357" t="n">
-        <v>1</v>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>000660SK HYNIX INC</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>2.23%21,113</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="K357" t="n">
-        <v>21113</v>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:20</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D358" t="n">
-        <v>2</v>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>2308台達電</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>-1.44%1710</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>-1.44%</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>2.05%441,000</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>2.05%</t>
-        </is>
-      </c>
-      <c r="K358" t="n">
-        <v>441000</v>
-      </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:20</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D359" t="n">
-        <v>2</v>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>6857ADVANTEST CORP</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>1.69%88,100</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="K359" t="n">
-        <v>88100</v>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:20</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D360" t="n">
-        <v>2</v>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>6274台燿</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>+2.06%1485</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>+2.06%</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>1.49%376,000</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="K360" t="n">
-        <v>376000</v>
-      </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:20</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D361" t="n">
-        <v>2</v>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>2454聯發科</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>-0.8%3735</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>1.43%142,000</t>
-        </is>
-      </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="K361" t="n">
-        <v>142000</v>
-      </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:21</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D362" t="n">
-        <v>3</v>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>6223旺矽</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>+0.63%5600</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
-      </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t>1.31%90,000</t>
-        </is>
-      </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>1.31%</t>
-        </is>
-      </c>
-      <c r="K362" t="n">
-        <v>90000</v>
-      </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:21</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D363" t="n">
-        <v>3</v>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>-0.17%591</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t>1.00%641,000</t>
-        </is>
-      </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="K363" t="n">
-        <v>641000</v>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:21</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D364" t="n">
-        <v>3</v>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>2345智邦</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>-1.93%2030</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>-1.93%</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>0.93%172,000</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>0.93%</t>
-        </is>
-      </c>
-      <c r="K364" t="n">
-        <v>172000</v>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:21</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D365" t="n">
-        <v>3</v>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>4062IBIDEN CO LTD</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>0.92%89,700</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="K365" t="n">
-        <v>89700</v>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:21</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D366" t="n">
-        <v>3</v>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>8046南電</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>+2.2%1160</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>+2.2%</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>0.91%302,000</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>0.91%</t>
-        </is>
-      </c>
-      <c r="K366" t="n">
-        <v>302000</v>
-      </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:10:21</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D367" t="n">
-        <v>3</v>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>2449京元電子</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>+0.21%239.5</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>239.5</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>0.62%1,008,000</t>
-        </is>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
-      </c>
-      <c r="K367" t="n">
-        <v>1008000</v>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M367" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M317"/>
+  <dimension ref="A1:M367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:04</t>
+          <t>2026-08-25 21:31:27</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:06</t>
+          <t>2026-08-25 21:31:29</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:07</t>
+          <t>2026-08-25 21:31:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:08</t>
+          <t>2026-08-25 21:31:31</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:08</t>
+          <t>2026-08-25 21:31:31</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:08</t>
+          <t>2026-08-25 21:31:31</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:08</t>
+          <t>2026-08-25 21:31:31</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:08</t>
+          <t>2026-08-25 21:31:31</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:24</t>
+          <t>2026-08-25 21:31:48</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:26</t>
+          <t>2026-08-25 21:31:49</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:27</t>
+          <t>2026-08-25 21:31:50</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:28</t>
+          <t>2026-08-25 21:31:51</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:28</t>
+          <t>2026-08-25 21:31:51</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:28</t>
+          <t>2026-08-25 21:31:51</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:28</t>
+          <t>2026-08-25 21:31:51</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:28</t>
+          <t>2026-08-25 21:31:51</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16313,17 +16313,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -16331,38 +16331,38 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2330台灣積體電路製造</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>-0.87%14285</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>14285</v>
+        <v>2400</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>8.77%260,000</t>
+          <t>13.92%588,000</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>13.92%</t>
         </is>
       </c>
       <c r="K261" t="n">
-        <v>260000</v>
+        <v>588000</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -16374,17 +16374,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -16392,38 +16392,38 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>2376技嘉科技</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>+1.05%2400</t>
+          <t>+1.91%347.5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>2400</v>
+        <v>347.5</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>7.40%1,306,000</t>
+          <t>4.92%1,448,000</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>4.92%</t>
         </is>
       </c>
       <c r="K262" t="n">
-        <v>1306000</v>
+        <v>1448000</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -16435,17 +16435,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -16453,38 +16453,38 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>+3.33%2950</t>
+          <t>-1.8%246</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>2950</v>
+        <v>246</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>6.97%1,001,000</t>
+          <t>4.34%1,737,000</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="K263" t="n">
-        <v>1001000</v>
+        <v>1737000</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -16496,17 +16496,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -16514,38 +16514,38 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>4904遠傳電信</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>+1.86%1095</t>
+          <t>+0.99%102.5</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>1095</v>
+        <v>102.5</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>6.42%2,482,000</t>
+          <t>3.88%3,832,000</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="K264" t="n">
-        <v>2482000</v>
+        <v>3832000</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -16557,17 +16557,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -16575,38 +16575,38 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2412中華電信</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>+3.04%5595</t>
+          <t>0%136.5</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>+3.04%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>5595</v>
+        <v>136.5</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>6.14%465,000</t>
+          <t>3.85%2,828,000</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="K265" t="n">
-        <v>465000</v>
+        <v>2828000</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -16618,17 +16618,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -16636,34 +16636,34 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>+1.22%2075</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>2075</v>
+        <v>6440</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>5.69%1,161,000</t>
+          <t>3.33%53,000</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K266" t="n">
-        <v>1161000</v>
+        <v>53000</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -16679,17 +16679,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -16715,20 +16715,20 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>5.15%1,074,000</t>
+          <t>2.56%124,000</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K267" t="n">
-        <v>1074000</v>
+        <v>124000</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -16740,17 +16740,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -16758,38 +16758,38 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>+6.11%1215</t>
+          <t>+0.97%5205</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>1215</v>
+        <v>5205</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>4.67%1,630,000</t>
+          <t>2.52%49,000</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K268" t="n">
-        <v>1630000</v>
+        <v>49000</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -16801,17 +16801,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -16819,38 +16819,38 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>1504東元電機</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>+6.22%5720</t>
+          <t>-0.98%70.8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>+6.22%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5720</v>
+        <v>70.8</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>4.63%343,000</t>
+          <t>2.47%3,473,000</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K269" t="n">
-        <v>343000</v>
+        <v>3473000</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -16862,17 +16862,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -16880,38 +16880,38 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3105穩懋半導體</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>+0.63%5600</t>
+          <t>+6.76%379</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+6.76%</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>5600</v>
+        <v>379</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>3.54%268,000</t>
+          <t>2.32%656,000</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K270" t="n">
-        <v>268000</v>
+        <v>656000</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -16923,17 +16923,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -16941,38 +16941,38 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>7750新代科技</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>+1.37%594</t>
+          <t>+9.81%2350</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>+1.37%</t>
+          <t>+9.81%</t>
         </is>
       </c>
       <c r="H271" t="n">
-        <v>594</v>
+        <v>2350</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>3.13%2,231,000</t>
+          <t>2.30%108,000</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K271" t="n">
-        <v>2231000</v>
+        <v>108000</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -16984,17 +16984,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -17002,38 +17002,38 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3081聯亞光電工業</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>+1.71%178.5</t>
+          <t>+7.05%2960</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+7.05%</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>178.5</v>
+        <v>2960</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>3.05%7,245,000</t>
+          <t>2.29%83,000</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K272" t="n">
-        <v>7245000</v>
+        <v>83000</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -17045,17 +17045,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -17063,38 +17063,38 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>+1.4%109</t>
+          <t>+9.93%1605</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H273" t="n">
-        <v>109</v>
+        <v>1605</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2.80%10,877,000</t>
+          <t>2.15%148,000</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K273" t="n">
-        <v>10877000</v>
+        <v>148000</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -17106,17 +17106,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -17124,38 +17124,38 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>+9.96%419.5</t>
+          <t>-0.78%50.6</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H274" t="n">
-        <v>419.5</v>
+        <v>50.6</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2.73%2,753,000</t>
+          <t>2.13%4,181,000</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K274" t="n">
-        <v>2753000</v>
+        <v>4181000</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -17167,17 +17167,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -17185,38 +17185,38 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>+3.99%404</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>+3.99%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>404</v>
+        <v>591</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2.56%2,682,000</t>
+          <t>1.98%335,000</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K275" t="n">
-        <v>2682000</v>
+        <v>335000</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -17228,17 +17228,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -17246,38 +17246,38 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>-1.44%1710</t>
+          <t>-0.72%6210</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>1710</v>
+        <v>6210</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2.55%632,000</t>
+          <t>1.93%31,000</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K276" t="n">
-        <v>632000</v>
+        <v>31000</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -17289,17 +17289,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -17307,38 +17307,38 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>+4.72%188.5</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>+4.72%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>188.5</v>
+        <v>2950</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2.42%5,445,000</t>
+          <t>1.93%68,000</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K277" t="n">
-        <v>5445000</v>
+        <v>68000</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -17350,17 +17350,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17386,16 +17386,16 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2.35%266,000</t>
+          <t>1.88%50,000</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="K278" t="n">
-        <v>266000</v>
+        <v>50000</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -17411,17 +17411,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -17429,38 +17429,38 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2610中華航空</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>+3.82%5570</t>
+          <t>-0.49%20.4</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>+3.82%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>5570</v>
+        <v>20.4</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>2.16%164,000</t>
+          <t>1.79%8,783,000</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K279" t="n">
-        <v>164000</v>
+        <v>8783000</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -17472,17 +17472,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -17490,38 +17490,38 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>+3.48%3865</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>+3.48%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>3865</v>
+        <v>1095</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>1.96%215,000</t>
+          <t>1.71%160,000</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K280" t="n">
-        <v>215000</v>
+        <v>160000</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -17533,17 +17533,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -17551,38 +17551,38 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>+5.16%835</t>
+          <t>+1.02%1490</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>+5.16%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>835</v>
+        <v>1490</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>1.66%844,013</t>
+          <t>1.59%108,000</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K281" t="n">
-        <v>844013</v>
+        <v>108000</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -17594,17 +17594,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -17612,38 +17612,38 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6147頎邦科技</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>+2.22%6440</t>
+          <t>+7.64%169</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>6440</v>
+        <v>169</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>1.17%77,000</t>
+          <t>1.59%1,019,000</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K282" t="n">
-        <v>77000</v>
+        <v>1019000</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -17655,17 +17655,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -17673,38 +17673,38 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>+1.95%444</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>444</v>
+        <v>14285</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>1.05%1,000,000</t>
+          <t>1.58%11,000</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K283" t="n">
-        <v>1000000</v>
+        <v>11000</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -17716,17 +17716,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -17734,38 +17734,38 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>-0.17%591</t>
+          <t>-1%198.5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>591</v>
+        <v>198.5</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>1.00%716,000</t>
+          <t>1.57%788,000</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K284" t="n">
-        <v>716000</v>
+        <v>788000</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -17777,17 +17777,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -17795,38 +17795,38 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>+2.2%1160</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>1160</v>
+        <v>1710</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>0.82%300,000</t>
+          <t>1.42%82,000</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K285" t="n">
-        <v>300000</v>
+        <v>82000</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -17838,17 +17838,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -17856,38 +17856,38 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>+9.84%530</t>
+          <t>+6.11%1215</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>+9.84%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>530</v>
+        <v>1215</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>0.47%373,000</t>
+          <t>1.29%113,000</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K286" t="n">
-        <v>373000</v>
+        <v>113000</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -17899,17 +17899,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -17917,34 +17917,34 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>+3.14%296</t>
+          <t>+0.65%77.9</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>+3.14%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>296</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>0.46%659,000</t>
+          <t>1.28%1,657,000</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K287" t="n">
-        <v>659000</v>
+        <v>1657000</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -17960,17 +17960,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -17978,38 +17978,38 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>+1.32%768</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H288" t="n">
-        <v>768</v>
+        <v>5595</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>0.45%250,000</t>
+          <t>1.24%23,000</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K288" t="n">
-        <v>250000</v>
+        <v>23000</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -18021,17 +18021,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -18039,38 +18039,38 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>+7.05%2960</t>
+          <t>+1.82%670</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>+7.05%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H289" t="n">
-        <v>2960</v>
+        <v>670</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>0.44%63,000</t>
+          <t>0.96%146,000</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K289" t="n">
-        <v>63000</v>
+        <v>146000</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -18082,17 +18082,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -18100,38 +18100,38 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>+0.22%925</t>
+          <t>+1.8%510</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>925</v>
+        <v>510</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>0.43%196,000</t>
+          <t>0.96%193,000</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K290" t="n">
-        <v>196000</v>
+        <v>193000</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -18143,17 +18143,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -18161,38 +18161,38 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>+1.91%347.5</t>
+          <t>+2.43%971</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>347.5</v>
+        <v>971</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>0.42%508,000</t>
+          <t>0.93%98,000</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K291" t="n">
-        <v>508000</v>
+        <v>98000</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -18204,17 +18204,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -18222,38 +18222,38 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>+0.97%5205</t>
+          <t>+5.39%1270</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H292" t="n">
-        <v>5205</v>
+        <v>1270</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>0.41%33,000</t>
+          <t>0.67%56,000</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K292" t="n">
-        <v>33000</v>
+        <v>56000</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -18265,17 +18265,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -18283,38 +18283,38 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>-0.23%87.5</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>87.5</v>
+        <v>5720</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>0.40%1,957,000</t>
+          <t>0.64%12,000</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K293" t="n">
-        <v>1957000</v>
+        <v>12000</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -18326,17 +18326,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -18344,38 +18344,38 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>+5.39%1270</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>1270</v>
+        <v>1160</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>0.40%134,000</t>
+          <t>0.54%48,000</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K294" t="n">
-        <v>134000</v>
+        <v>48000</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -18387,17 +18387,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -18405,38 +18405,38 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>+1.89%15400</t>
+          <t>-1.27%544</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>+1.89%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>15400</v>
+        <v>544</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>0.40%11,000</t>
+          <t>0.49%89,000</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K295" t="n">
-        <v>11000</v>
+        <v>89000</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -18448,17 +18448,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -18466,34 +18466,34 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>+2.06%1485</t>
+          <t>+1.95%444</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>+2.06%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>1485</v>
+        <v>444</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>0.40%113,000</t>
+          <t>0.48%110,000</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K296" t="n">
-        <v>113000</v>
+        <v>110000</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -18509,17 +18509,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -18527,38 +18527,38 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>+0.47%1070</t>
+          <t>-2.34%2085</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>1070</v>
+        <v>2085</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>0.39%155,000</t>
+          <t>0.43%20,000</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K297" t="n">
-        <v>155000</v>
+        <v>20000</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -18570,17 +18570,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -18588,38 +18588,38 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>-2.33%628</t>
+          <t>+1.13%179</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>628</v>
+        <v>179</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>0.39%261,000</t>
+          <t>0.43%243,000</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K298" t="n">
-        <v>261000</v>
+        <v>243000</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -18631,17 +18631,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -18649,38 +18649,38 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3131弘塑科技</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>-5.07%1965</t>
+          <t>-3.21%2260</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>-5.07%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>1965</v>
+        <v>2260</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>0.35%76,000</t>
+          <t>0.28%12,000</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K299" t="n">
-        <v>76000</v>
+        <v>12000</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -18692,17 +18692,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -18710,38 +18710,38 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>-3.82%1510</t>
+          <t>+1.21%125</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>1510</v>
+        <v>125</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>0.35%98,000</t>
+          <t>0.21%171,000</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K300" t="n">
-        <v>98000</v>
+        <v>171000</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -18753,17 +18753,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -18771,38 +18771,38 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>1802台灣玻璃工業</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>-0.33%150.5</t>
+          <t>+1.93%58</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>150.5</v>
+        <v>58</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>0.22%629,000</t>
+          <t>0.20%357,000</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K301" t="n">
-        <v>629000</v>
+        <v>357000</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -18814,58 +18814,56 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
+          <t>2881富邦金融控股</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.2%141.5</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>141.5</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>3.54%935,600</t>
+          <t>0.20%154,000</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K302" t="n">
-        <v>935600</v>
+        <v>154000</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -18877,58 +18875,56 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>009150SAMSUNG ELECTRO-MECHANICS CO</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.42%64.5</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.42%</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>64.5</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>3.39%42,083</t>
+          <t>0.19%306,000</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K303" t="n">
-        <v>42083</v>
+        <v>306000</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -18940,58 +18936,56 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2049上銀科技</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>+1.86%1095</t>
+          <t>+0.58%345.5</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>+1.86%</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>1095</t>
-        </is>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>345.5</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>3.30%1,146,000</t>
+          <t>0.19%55,000</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K304" t="n">
-        <v>1146000</v>
+        <v>55000</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -19003,58 +18997,56 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>+3.04%5595</t>
+          <t>-0.23%2195</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>+3.04%</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>5595</t>
-        </is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>2195</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>3.20%212,000</t>
+          <t>0.18%8,000</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K305" t="n">
-        <v>212000</v>
+        <v>8000</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -19066,58 +19058,56 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>+1.05%2400</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>+1.05%</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>2075</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>2.60%406,000</t>
+          <t>0.18%9,000</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K306" t="n">
-        <v>406000</v>
+        <v>9000</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -19129,58 +19119,56 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>000660SK HYNIX INC</t>
+          <t>2317鴻海精密工業</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.21%243</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>243</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>2.23%21,113</t>
+          <t>0.16%64,000</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K307" t="n">
-        <v>21113</v>
+        <v>64000</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -19192,58 +19180,56 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>-1.44%1710</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>-1.44%</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+          <t>-5.07%</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>1965</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>2.05%441,000</t>
+          <t>0.10%5,000</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K308" t="n">
-        <v>441000</v>
+        <v>5000</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -19255,58 +19241,56 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>6857ADVANTEST CORP</t>
+          <t>6488環球晶圓</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.97%980</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.97%</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>980</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>1.69%88,100</t>
+          <t>0.10%10,000</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K309" t="n">
-        <v>88100</v>
+        <v>10000</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -19318,58 +19302,56 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>+2.06%1485</t>
+          <t>+5.16%835</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>+2.06%</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
+          <t>+5.16%</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>835</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>1.49%376,000</t>
+          <t>0.02%2,000</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K310" t="n">
-        <v>376000</v>
+        <v>2000</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -19381,58 +19363,56 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>-0.8%3735</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>14285</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>1.43%142,000</t>
+          <t>8.77%260,000</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="K311" t="n">
-        <v>142000</v>
+        <v>260000</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -19444,58 +19424,56 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>+0.63%5600</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
+          <t>+1.05%</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>2400</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>1.31%90,000</t>
+          <t>7.40%1,306,000</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>7.40%</t>
         </is>
       </c>
       <c r="K312" t="n">
-        <v>90000</v>
+        <v>1306000</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -19507,58 +19485,56 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>-0.17%591</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+          <t>+3.33%</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>2950</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>1.00%641,000</t>
+          <t>6.97%1,001,000</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="K313" t="n">
-        <v>641000</v>
+        <v>1001000</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -19570,58 +19546,56 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>-1.93%2030</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>-1.93%</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
+          <t>+1.86%</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>1095</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>0.93%172,000</t>
+          <t>6.42%2,482,000</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>6.42%</t>
         </is>
       </c>
       <c r="K314" t="n">
-        <v>172000</v>
+        <v>2482000</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -19633,58 +19607,56 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.04%</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>5595</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>0.92%89,700</t>
+          <t>6.14%465,000</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="K315" t="n">
-        <v>89700</v>
+        <v>465000</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -19696,58 +19668,56 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>+2.2%1160</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>+2.2%</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>2075</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>0.91%302,000</t>
+          <t>5.69%1,161,000</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>5.69%</t>
         </is>
       </c>
       <c r="K316" t="n">
-        <v>302000</v>
+        <v>1161000</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -19759,61 +19729,3141 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-1.93%2030</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-1.93%</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>2030</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>5.15%1,074,000</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>5.15%</t>
+        </is>
+      </c>
+      <c r="K317" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>8996高力</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>+6.11%1215</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>+6.11%</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>1215</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>4.67%1,630,000</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>4.67%</t>
+        </is>
+      </c>
+      <c r="K318" t="n">
+        <v>1630000</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>+6.22%5720</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>+6.22%</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>5720</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>4.63%343,000</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>4.63%</t>
+        </is>
+      </c>
+      <c r="K319" t="n">
+        <v>343000</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>+0.63%5600</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>3.54%268,000</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="K320" t="n">
+        <v>268000</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>6584南俊國際</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>+1.37%594</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>+1.37%</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>594</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>3.13%2,231,000</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="K321" t="n">
+        <v>2231000</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>3231緯創</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>+1.71%178.5</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>+1.71%</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>3.05%7,245,000</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="K322" t="n">
+        <v>7245000</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>1</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>1815富喬</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>+1.4%109</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>109</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>2.80%10,877,000</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>2.80%</t>
+        </is>
+      </c>
+      <c r="K323" t="n">
+        <v>10877000</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2455全新</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>+9.96%419.5</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>+9.96%</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>2.73%2,753,000</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="K324" t="n">
+        <v>2753000</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:08</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>8021尖點</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>+3.99%404</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>+3.99%</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>404</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>2.56%2,682,000</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="K325" t="n">
+        <v>2682000</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>2</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-1.44%1710</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>1710</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>2.55%632,000</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="K326" t="n">
+        <v>632000</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>2</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>1303南亞</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>+4.72%188.5</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>+4.72%</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>2.42%5,445,000</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="K327" t="n">
+        <v>5445000</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>2</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-0.8%3735</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>3735</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>2.35%266,000</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
+      </c>
+      <c r="K328" t="n">
+        <v>266000</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>2</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>3443創意</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>+3.82%5570</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>+3.82%</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>5570</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>2.16%164,000</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="K329" t="n">
+        <v>164000</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>2</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>3661世芯-KY</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>+3.48%3865</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>+3.48%</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>3865</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>1.96%215,000</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="K330" t="n">
+        <v>215000</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>2</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>3189景碩</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>+5.16%835</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>+5.16%</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>835</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>1.66%844,013</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="K331" t="n">
+        <v>844013</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>2</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>6669緯穎</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>+2.22%6440</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>+2.22%</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>6440</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>1.17%77,000</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="K332" t="n">
+        <v>77000</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>2</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>4958臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>+1.95%444</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>+1.95%</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>444</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>1.05%1,000,000</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="K333" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>2</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-0.17%591</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>591</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>1.00%716,000</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="K334" t="n">
+        <v>716000</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>2</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>8046南電</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>+2.2%1160</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>1160</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>0.82%300,000</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="K335" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>2</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>6213聯茂</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>+9.84%530</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>+9.84%</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>530</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>0.47%373,000</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="K336" t="n">
+        <v>373000</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>2</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2301光寶科</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>+3.14%296</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>+3.14%</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>296</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>0.46%659,000</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="K337" t="n">
+        <v>659000</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>2</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>6139亞翔</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>+1.32%768</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>+1.32%</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>768</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>0.45%250,000</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="K338" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>2</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>3081聯亞</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>+7.05%2960</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>+7.05%</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>2960</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>0.44%63,000</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="K339" t="n">
+        <v>63000</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:09</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>2</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2357華碩</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>+0.22%925</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>925</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>0.43%196,000</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="K340" t="n">
+        <v>196000</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>3</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2376技嘉</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>+1.91%347.5</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>+1.91%</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>0.42%508,000</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="K341" t="n">
+        <v>508000</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>3</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>3653健策</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>+0.97%5205</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>5205</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>0.41%33,000</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="K342" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>3</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>8150南茂</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-0.23%87.5</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>0.40%1,957,000</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K343" t="n">
+        <v>1957000</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>3</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>6187萬潤</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>+5.39%1270</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>+5.39%</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>1270</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>0.40%134,000</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K344" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>3</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>5274信驊</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>+1.89%15400</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>+1.89%</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>15400</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>0.40%11,000</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K345" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>3</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>+2.06%1485</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>+2.06%</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>1485</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>0.40%113,000</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K346" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>3</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2404漢唐</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>+0.47%1070</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>+0.47%</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>1070</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>0.39%155,000</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="K347" t="n">
+        <v>155000</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>3</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>3026禾伸堂</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-2.33%628</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-2.33%</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>628</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>0.39%261,000</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="K348" t="n">
+        <v>261000</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>3</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-5.07%1965</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-5.07%</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>1965</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>0.35%76,000</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="K349" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>3</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>5289宜鼎</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-3.82%1510</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-3.82%</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>1510</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>0.35%98,000</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="K350" t="n">
+        <v>98000</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:11</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>3</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>5347世界</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-0.33%150.5</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>0.22%629,000</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="K351" t="n">
+        <v>629000</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
           <t>00990A</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-08-25 21:29:46</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:15</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
         <is>
           <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
-      <c r="D317" t="n">
+      <c r="D352" t="n">
+        <v>1</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>3.54%935,600</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="K352" t="n">
+        <v>935600</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:15</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>009150SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>3.39%42,083</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="K353" t="n">
+        <v>42083</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:15</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>3037欣興</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>+1.86%1095</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>+1.86%</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>3.30%1,146,000</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="K354" t="n">
+        <v>1146000</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:15</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2383台光電</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>+3.04%5595</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>+3.04%</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>3.20%212,000</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>3.20%</t>
+        </is>
+      </c>
+      <c r="K355" t="n">
+        <v>212000</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:15</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2330台積電</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>+1.05%2400</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>+1.05%</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>2.60%406,000</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="K356" t="n">
+        <v>406000</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:15</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>1</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>000660SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>2.23%21,113</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="K357" t="n">
+        <v>21113</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:17</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>2</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-1.44%1710</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2.05%441,000</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="K358" t="n">
+        <v>441000</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:17</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>2</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>6857ADVANTEST CORP</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>1.69%88,100</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="K359" t="n">
+        <v>88100</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:17</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>2</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>+2.06%1485</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>+2.06%</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>1.49%376,000</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="K360" t="n">
+        <v>376000</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:17</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>2</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-0.8%3735</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>1.43%142,000</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="K361" t="n">
+        <v>142000</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:18</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
         <v>3</v>
       </c>
-      <c r="E317" t="inlineStr">
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>+0.63%5600</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>1.31%90,000</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="K362" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:18</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>3</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-0.17%591</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>1.00%641,000</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="K363" t="n">
+        <v>641000</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:18</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>3</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-1.93%2030</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-1.93%</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>0.93%172,000</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="K364" t="n">
+        <v>172000</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:18</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>3</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>4062IBIDEN CO LTD</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>0.92%89,700</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="K365" t="n">
+        <v>89700</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:18</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>3</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>8046南電</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>+2.2%1160</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>0.91%302,000</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="K366" t="n">
+        <v>302000</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-08-25 21:32:18</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>3</v>
+      </c>
+      <c r="E367" t="inlineStr">
         <is>
           <t>2449京元電子</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
+      <c r="F367" t="inlineStr">
         <is>
           <t>+0.21%239.5</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
+      <c r="G367" t="inlineStr">
         <is>
           <t>+0.21%</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
+      <c r="H367" t="inlineStr">
         <is>
           <t>239.5</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr">
+      <c r="I367" t="inlineStr">
         <is>
           <t>0.62%1,008,000</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr">
+      <c r="J367" t="inlineStr">
         <is>
           <t>0.62%</t>
         </is>
       </c>
-      <c r="K317" t="n">
+      <c r="K367" t="n">
         <v>1008000</v>
       </c>
-      <c r="L317" t="inlineStr">
+      <c r="L367" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
+      <c r="M367" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-25_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:27</t>
+          <t>2026-08-25 22:04:12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:29</t>
+          <t>2026-08-25 22:04:13</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:30</t>
+          <t>2026-08-25 22:04:15</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:31</t>
+          <t>2026-08-25 22:04:16</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:31</t>
+          <t>2026-08-25 22:04:16</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:31</t>
+          <t>2026-08-25 22:04:16</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:31</t>
+          <t>2026-08-25 22:04:16</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:31</t>
+          <t>2026-08-25 22:04:16</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:48</t>
+          <t>2026-08-25 22:04:31</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:49</t>
+          <t>2026-08-25 22:04:32</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:50</t>
+          <t>2026-08-25 22:04:33</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:51</t>
+          <t>2026-08-25 22:04:35</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:51</t>
+          <t>2026-08-25 22:04:35</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:51</t>
+          <t>2026-08-25 22:04:35</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:51</t>
+          <t>2026-08-25 22:04:35</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:51</t>
+          <t>2026-08-25 22:04:35</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22247,7 +22247,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22751,7 +22751,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
